--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_quarterly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,81 +982,85 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39364</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40486</v>
-      </c>
+        <v>44848</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>775</v>
+        <v>1474</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4325761954003344</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4325761954003344</v>
       </c>
       <c r="P4" t="n">
-        <v>774</v>
+        <v>1474</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1532547245176263</v>
+        <v>0.2765764911333392</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
       <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-0.07834419810291049</v>
+      </c>
       <c r="U4" t="n">
-        <v>355</v>
+        <v>670</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4325761954003344</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4325761954003344</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>420</v>
+        <v>804</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.7623511595632295</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
@@ -1068,19 +1072,19 @@
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,67 +1141,67 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>36521</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38994</v>
+      </c>
       <c r="M5" t="n">
-        <v>1474</v>
+        <v>1703</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.4325761954003344</v>
+        <v>-0.4324636107084076</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.4325761954003344</v>
+        <v>-0.4324636107084076</v>
       </c>
       <c r="P5" t="n">
-        <v>1474</v>
+        <v>1702</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2765764911333392</v>
+        <v>0.2101877592900238</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>-0.07834419810291049</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.4325761954003344</v>
+        <v>-0.4324636107084076</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.4325761954003344</v>
+        <v>-0.4324636107084076</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>804</v>
+        <v>1059</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.7623511595632295</v>
+        <v>0.7620015542055643</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
@@ -1209,11 +1213,11 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
@@ -1225,19 +1229,19 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,24 +1277,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -1300,22 +1300,22 @@
         <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38994</v>
+        <v>41393</v>
       </c>
       <c r="M6" t="n">
-        <v>1703</v>
+        <v>3354</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4324636107084076</v>
+        <v>-0.6167887185672993</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4324636107084076</v>
+        <v>-0.6167887185672993</v>
       </c>
       <c r="P6" t="n">
-        <v>1702</v>
+        <v>3353</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2101877592900238</v>
+        <v>0.3571118946009312</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1329,21 +1329,21 @@
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.4324636107084076</v>
+        <v>-0.6167887185672993</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.4324636107084076</v>
+        <v>-0.6167887185672993</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1059</v>
+        <v>2710</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.7620015542055643</v>
+        <v>1.609526515663447</v>
       </c>
       <c r="AD6" s="3" t="n">
         <v>0.5</v>
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
@@ -1386,37 +1386,19 @@
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,7 +1439,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -1467,22 +1449,22 @@
         <v>37460</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>41393</v>
+        <v>40567</v>
       </c>
       <c r="M7" t="n">
-        <v>3354</v>
+        <v>2786</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.6167887185672993</v>
+        <v>-0.5687350964668526</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.6167887185672993</v>
+        <v>-0.5687350964668526</v>
       </c>
       <c r="P7" t="n">
-        <v>3353</v>
+        <v>2785</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3571118946009312</v>
+        <v>0.3013280451563845</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1496,21 +1478,21 @@
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>-0.6167887185672993</v>
+        <v>-0.5687350964668526</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.6167887185672993</v>
+        <v>-0.5687350964668526</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2710</v>
+        <v>2142</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>1.609526515663447</v>
+        <v>1.318760445859326</v>
       </c>
       <c r="AD7" s="3" t="n">
         <v>0.5</v>
@@ -1529,11 +1511,11 @@
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
@@ -1553,11 +1535,11 @@
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36521</v>
+        <v>36770</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>37838</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40567</v>
+        <v>40133</v>
       </c>
       <c r="M8" t="n">
-        <v>2786</v>
+        <v>2314</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5687350964668526</v>
+        <v>-0.386058675102369</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5687350964668526</v>
+        <v>-0.386058675102369</v>
       </c>
       <c r="P8" t="n">
-        <v>2785</v>
+        <v>2313</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3013280451563845</v>
+        <v>0.235360901568436</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,98 +1623,80 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>644</v>
+        <v>731</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.5687350964668526</v>
+        <v>-0.386058675102369</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.5687350964668526</v>
+        <v>-0.386058675102369</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2142</v>
+        <v>1583</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>1.318760445859326</v>
+        <v>0.6288201485162133</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
       <c r="AL8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36770</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37838</v>
+        <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40133</v>
+        <v>39279</v>
       </c>
       <c r="M9" t="n">
-        <v>2314</v>
+        <v>1723</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.386058675102369</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.386058675102369</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="P9" t="n">
-        <v>2313</v>
+        <v>1722</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.235360901568436</v>
+        <v>0.2586600843786702</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,25 +1772,25 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>731</v>
+        <v>470</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.386058675102369</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.386058675102369</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1583</v>
+        <v>1253</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.6288201485162133</v>
+        <v>0.9834344794881269</v>
       </c>
       <c r="AD9" s="3" t="n">
         <v>0.6666666666666666</v>
@@ -1849,11 +1809,11 @@
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
@@ -1873,11 +1833,11 @@
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36770</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>39279</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1723</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1722</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2586600843786702</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>470</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1253</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.9834344794881269</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2546,7 +2335,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2556,7 +2345,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2567,41 +2356,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36880</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37776</v>
+        <v>38922</v>
       </c>
       <c r="M4" t="n">
-        <v>801</v>
+        <v>1591</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.2056920481641104</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="P4" t="n">
-        <v>276</v>
+        <v>1583</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1192072642606282</v>
+        <v>0.1543707126316287</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.07750973284135629</v>
+        <v>0.1414173762065351</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2614,35 +2407,35 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>189</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-449</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2100718359282402</v>
+        <v>-0.2056920481641104</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3100613758801871</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>218</v>
+        <v>1402</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2659378985114353</v>
+        <v>0.2589575588267659</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.2486028467031714</v>
+        <v>-0.1846952033379927</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3213393457552459</v>
+        <v>0.3257191335193758</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
@@ -2663,7 +2456,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2694,35 +2487,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36880</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38922</v>
+        <v>38958</v>
       </c>
       <c r="M5" t="n">
-        <v>1591</v>
+        <v>1617</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2056920481641104</v>
+        <v>-0.4211034935649058</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.4324281870017384</v>
       </c>
       <c r="P5" t="n">
-        <v>1583</v>
+        <v>1609</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1543707126316287</v>
+        <v>0.2150499661001916</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1414173762065351</v>
+        <v>0.1986071921955756</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2735,35 +2528,35 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>189</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-449</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2056920481641104</v>
+        <v>-0.4211034935649058</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.4324281870017384</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1402</v>
+        <v>1034</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2589575588267659</v>
+        <v>0.7274244858689951</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1846952033379927</v>
+        <v>-0.1275053873489521</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3257191335193758</v>
+        <v>0.1103076881185803</v>
       </c>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
@@ -2784,7 +2577,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2802,24 +2595,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -2828,26 +2617,24 @@
       <c r="K6" s="2" t="n">
         <v>37460</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>38958</v>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1617</v>
+        <v>1896</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4211034935649058</v>
+        <v>-0.6091181530671368</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="P6" t="n">
-        <v>1609</v>
+        <v>1889</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.2150499661001916</v>
+        <v>0.4367609404936754</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1986071921955756</v>
+        <v>0.4367609404936754</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2856,9 +2643,11 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.2595369962595653</v>
+      </c>
       <c r="W6" t="n">
         <v>583</v>
       </c>
@@ -2866,46 +2655,38 @@
         <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4211034935649058</v>
+        <v>-0.6091181530671368</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1034</v>
+        <v>1313</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.7274244858689951</v>
+        <v>1.558317834012275</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.1275053873489521</v>
+        <v>0.1106483609491477</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1103076881185803</v>
+        <v>-0.07770697138365068</v>
       </c>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
         <v>1</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.1210974593542193</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.2110316576366656</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>816</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2917,7 +2698,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2948,7 +2729,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -2962,19 +2743,19 @@
         <v>1896</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.6091181530671368</v>
+        <v>-0.5601026635225388</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="P7" t="n">
         <v>1889</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.4367609404936754</v>
+        <v>0.3387659126715243</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.4367609404936754</v>
+        <v>0.3387659126715243</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>39364</v>
@@ -2986,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-0.2595369962595653</v>
+        <v>-0.08001949728659474</v>
       </c>
       <c r="W7" t="n">
         <v>583</v>
@@ -2995,10 +2776,10 @@
         <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.6091181530671368</v>
+        <v>-0.5601026635225388</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
@@ -3011,13 +2792,13 @@
         <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.558317834012275</v>
+        <v>1.273257683275917</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1106483609491477</v>
+        <v>0.01265333312699657</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.07770697138365068</v>
+        <v>-0.02869148183905268</v>
       </c>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
@@ -3038,7 +2819,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3056,50 +2837,46 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>37838</v>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
         <v>1896</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.5601026635225388</v>
+        <v>-0.3560213736027806</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.3860586751023685</v>
       </c>
       <c r="P8" t="n">
-        <v>1889</v>
+        <v>1766</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.3387659126715243</v>
+        <v>0.2569514384238935</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.3387659126715243</v>
+        <v>0.2569514384238935</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3111,53 +2888,47 @@
         <v>1</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>-0.08001949728659474</v>
+        <v>-0.02047746840375408</v>
       </c>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>844</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5601026635225388</v>
+        <v>-0.3560213736027806</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.3860586751023685</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1313</v>
+        <v>1052</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.273257683275917</v>
+        <v>0.5528465682076524</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.01265333312699657</v>
+        <v>-0.06916114112063426</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.02869148183905268</v>
+        <v>0.1753898080807055</v>
       </c>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
         <v>1</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.261256179830168</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.3500308275942986</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="b">
-        <v>1</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -3169,7 +2940,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3200,33 +2971,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37838</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>39066</v>
+      </c>
       <c r="M9" t="n">
-        <v>1896</v>
+        <v>1693</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.3560213736027806</v>
+        <v>-0.4659826112756107</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3860586751023685</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="P9" t="n">
-        <v>1766</v>
+        <v>1597</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2569514384238935</v>
+        <v>0.2604511098226162</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2569514384238935</v>
+        <v>0.2461213280970662</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3235,41 +3008,39 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.02047746840375408</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>844</v>
+        <v>583</v>
       </c>
       <c r="X9" t="n">
-        <v>206</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3560213736027806</v>
+        <v>-0.4659826112756107</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3860586751023685</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1052</v>
+        <v>1110</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.5528465682076524</v>
+        <v>0.8725981983259128</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06916114112063426</v>
+        <v>-0.07999125144746153</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1753898080807055</v>
+        <v>0.06542857040787542</v>
       </c>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
@@ -3281,139 +3052,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>39066</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1693</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4659826112756107</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1597</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2604511098226162</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.2461213280970662</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.4659826112756107</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4958240313246576</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1110</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.8725981983259128</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.07999125144746153</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.06542857040787542</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.1686115952557099</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.2559107753473705</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>892</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3426,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3909,7 +3547,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3919,7 +3557,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3930,41 +3568,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>41061</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40486</v>
+        <v>41117</v>
       </c>
       <c r="M4" t="n">
-        <v>775</v>
+        <v>1210</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.08555079627746587</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="P4" t="n">
-        <v>774</v>
+        <v>249</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1532547245176266</v>
+        <v>0.04332405449145316</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.08127722777506252</v>
+        <v>0.02870286938692595</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -3977,40 +3619,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>1171</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.08555079627746587</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>420</v>
+        <v>39</v>
       </c>
       <c r="AC4" t="n">
-        <v>-440</v>
+        <v>-821</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.0935544543417024</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03573767042322865</v>
+        <v>-0.08831202881136521</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.07437696358203638</v>
+        <v>0.3563260434991777</v>
       </c>
       <c r="AH4" t="n">
-        <v>-55</v>
+        <v>-436</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4019,8 +3661,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1475930532307546</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1079725986742808</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4030,7 +3676,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4061,35 +3707,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>41061</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>41117</v>
+        <v>40486</v>
       </c>
       <c r="M5" t="n">
-        <v>1210</v>
+        <v>775</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.08555079627746587</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1365494988551755</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="P5" t="n">
-        <v>249</v>
+        <v>774</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04332405449145316</v>
+        <v>0.1532547245176266</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02870286938692595</v>
+        <v>0.08127722777506252</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4102,40 +3748,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>1171</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>816</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.08555079627746587</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1365494988551755</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>39</v>
+        <v>420</v>
       </c>
       <c r="AC5" t="n">
-        <v>-821</v>
+        <v>-440</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.0935544543417024</v>
+        <v>0.5810273585142876</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.08831202881136521</v>
+        <v>-0.03573767042322865</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3563260434991777</v>
+        <v>0.07437696358203638</v>
       </c>
       <c r="AH5" t="n">
-        <v>-436</v>
+        <v>-55</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4148,7 +3794,7 @@
         <v>0.1475930532307546</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1079725986742808</v>
+        <v>-0.007539848144645811</v>
       </c>
     </row>
     <row r="6">
@@ -4159,7 +3805,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4177,24 +3823,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -4204,25 +3846,25 @@
         <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40486</v>
+        <v>40095</v>
       </c>
       <c r="M6" t="n">
-        <v>775</v>
+        <v>505</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="P6" t="n">
-        <v>774</v>
+        <v>490</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1532547245176266</v>
+        <v>0.06488886565424552</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.08127722777506252</v>
+        <v>0.0277887870264453</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4241,56 +3883,44 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="AC6" t="n">
-        <v>-440</v>
+        <v>-710</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.2909038630923371</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03573767042322865</v>
+        <v>-0.08922611117184587</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.07437696358203638</v>
+        <v>0.2165278642181678</v>
       </c>
       <c r="AH6" t="n">
-        <v>-55</v>
+        <v>-325</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.007539848144645811</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4300,7 +3930,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4331,7 +3961,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -4341,25 +3971,25 @@
         <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40095</v>
+        <v>40449</v>
       </c>
       <c r="M7" t="n">
-        <v>505</v>
+        <v>748</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2253489755584758</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="P7" t="n">
-        <v>490</v>
+        <v>733</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06488886565424552</v>
+        <v>0.1500396731487487</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0277887870264453</v>
+        <v>0.0781755900741586</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4378,34 +4008,34 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2253489755584758</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>150</v>
+        <v>393</v>
       </c>
       <c r="AC7" t="n">
-        <v>-710</v>
+        <v>-467</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2909038630923371</v>
+        <v>0.5722881401796749</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.08922611117184587</v>
+        <v>-0.03883930812413257</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2165278642181678</v>
+        <v>0.07789257661589999</v>
       </c>
       <c r="AH7" t="n">
-        <v>-325</v>
+        <v>-82</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4425,7 +4055,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4443,52 +4073,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>39412</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40449</v>
+        <v>39428</v>
       </c>
       <c r="M8" t="n">
-        <v>748</v>
+        <v>45</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3639842631607436</v>
+        <v>-0.05542135568040074</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="P8" t="n">
-        <v>733</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1500396731487487</v>
+        <v>0.03285628964813481</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0781755900741586</v>
+        <v>0.004242497392177237</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4501,56 +4127,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>33</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3639842631607436</v>
+        <v>-0.05542135568040074</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>393</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>-467</v>
+        <v>-848</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.5722881401796749</v>
+        <v>0.05867309833192547</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03883930812413257</v>
+        <v>-0.1127724008061139</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07789257661589999</v>
+        <v>0.3864554840962429</v>
       </c>
       <c r="AH8" t="n">
-        <v>-82</v>
+        <v>-463</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.003101637700903923</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0.003515613033863607</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-27</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4562,7 +4180,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4593,35 +4211,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>39412</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>39428</v>
+        <v>40445</v>
       </c>
       <c r="M9" t="n">
-        <v>45</v>
+        <v>746</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.05542135568040074</v>
+        <v>-0.3561271102519856</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.06689328315495324</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>731</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.03285628964813481</v>
+        <v>0.1489538204488156</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.004242497392177237</v>
+        <v>0.07750613802078468</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4634,40 +4252,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>-322</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.05542135568040074</v>
+        <v>-0.3561271102519856</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.06689328315495324</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>12</v>
+        <v>391</v>
       </c>
       <c r="AC9" t="n">
-        <v>-848</v>
+        <v>-469</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.05867309833192547</v>
+        <v>0.5531015762930465</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1127724008061139</v>
+        <v>-0.03950876017750649</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3864554840962429</v>
+        <v>0.08574972952465798</v>
       </c>
       <c r="AH9" t="n">
-        <v>-463</v>
+        <v>-84</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4678,143 +4296,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40445</v>
-      </c>
-      <c r="M10" t="n">
-        <v>746</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3561271102519856</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3639469600214459</v>
-      </c>
-      <c r="P10" t="n">
-        <v>731</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1489538204488156</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.07750613802078468</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3561271102519856</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3639469600214459</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>391</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-469</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.5531015762930465</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.03950876017750649</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.08574972952465798</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-84</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.00377108975427784</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0.0113727659426216</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-29</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4827,7 +4308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5310,7 +4791,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5320,7 +4801,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5331,13 +4812,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5347,25 +4832,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43560</v>
+        <v>43578</v>
       </c>
       <c r="M4" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.1968052513911283</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1971519721341342</v>
       </c>
       <c r="P4" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04801488482583489</v>
+        <v>0.07990143847314349</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02965112288406209</v>
+        <v>0.05131323495950512</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5384,34 +4869,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1350492147242662</v>
+        <v>-0.1968052513911283</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1424709615053656</v>
+        <v>-0.1971519721341342</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1561351432049565</v>
+        <v>0.2450280604199588</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02120805059514199</v>
+        <v>0.0004540614803010407</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.05795653325116323</v>
+        <v>-0.003799503415698791</v>
       </c>
       <c r="AH4" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5420,8 +4905,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.2004725031597112</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1592411666562514</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5431,7 +4920,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5462,7 +4951,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5472,25 +4961,25 @@
         <v>43458</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43578</v>
+        <v>43588</v>
       </c>
       <c r="M5" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1968052513911283</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="P5" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.07990143847314349</v>
+        <v>0.08303743446013791</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.05131323495950512</v>
+        <v>0.05476872768330868</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43880</v>
@@ -5509,34 +4998,34 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1968052513911283</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.2026163801193157</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AC5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2450280604199588</v>
+        <v>0.2541015078158164</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.0004540614803010407</v>
+        <v>0.003909554204104604</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.003799503415698791</v>
+        <v>-0.009610632143886244</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5549,7 +5038,7 @@
         <v>0.2004725031597112</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1592411666562514</v>
+        <v>-0.01980775507866428</v>
       </c>
     </row>
     <row r="6">
@@ -5560,7 +5049,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5578,24 +5067,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -5605,25 +5090,25 @@
         <v>43458</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43588</v>
+        <v>43815</v>
       </c>
       <c r="M6" t="n">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="P6" t="n">
-        <v>152</v>
+        <v>304</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.08303743446013791</v>
+        <v>0.09948481923745864</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05476872768330868</v>
+        <v>0.0932471095787893</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5642,56 +5127,44 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2541015078158164</v>
+        <v>0.2391661991287057</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.003909554204104604</v>
+        <v>0.04238793609958522</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.009610632143886244</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.0251176047992466</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.06756716539504948</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.2004725031597112</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.01980775507866428</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5701,7 +5174,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5732,7 +5205,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -5742,10 +5215,10 @@
         <v>43458</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43815</v>
+        <v>43655</v>
       </c>
       <c r="M7" t="n">
-        <v>310</v>
+        <v>198</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>-0.1930057479754295</v>
@@ -5754,13 +5227,13 @@
         <v>-0.1964175293895148</v>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.09948481923745864</v>
+        <v>0.07880862330706591</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0932471095787893</v>
+        <v>0.05908791263210079</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5788,10 +5261,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>246</v>
+        <v>134</v>
       </c>
       <c r="AC7" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
@@ -5800,13 +5273,13 @@
         <v>0.2391661991287057</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.04238793609958522</v>
+        <v>0.008228739152896715</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5826,7 +5299,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5844,24 +5317,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -5871,25 +5340,25 @@
         <v>43458</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43655</v>
+        <v>43815</v>
       </c>
       <c r="M8" t="n">
-        <v>198</v>
+        <v>310</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.1930057479754296</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.196417529389515</v>
       </c>
       <c r="P8" t="n">
-        <v>192</v>
+        <v>304</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.07880862330706591</v>
+        <v>0.09948481923745901</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05908791263210079</v>
+        <v>0.09324710957878965</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5908,50 +5377,42 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.1930057479754296</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.196417529389515</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>134</v>
+        <v>246</v>
       </c>
       <c r="AC8" t="n">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.239166199128706</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.008228739152896715</v>
+        <v>0.04238793609958557</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.02943678974803871</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.05795653325116323</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>64</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5963,7 +5424,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5994,7 +5455,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -6004,25 +5465,25 @@
         <v>43458</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43815</v>
+        <v>43655</v>
       </c>
       <c r="M9" t="n">
-        <v>310</v>
+        <v>198</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1930057479754296</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="P9" t="n">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.09948481923745901</v>
+        <v>0.07880862330706591</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.09324710957878965</v>
+        <v>0.05908791263210079</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6041,34 +5502,34 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1930057479754296</v>
+        <v>-0.1930057479754295</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>246</v>
+        <v>134</v>
       </c>
       <c r="AC9" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.239166199128706</v>
+        <v>0.2391661991287057</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.04238793609958557</v>
+        <v>0.008228739152896715</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>166</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6079,143 +5540,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43655</v>
-      </c>
-      <c r="M10" t="n">
-        <v>198</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1930057479754295</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1964175293895148</v>
-      </c>
-      <c r="P10" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.07880862330706591</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05908791263210079</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1930057479754295</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1964175293895148</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>134</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>58</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2391661991287057</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.008228739152896715</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>54</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.02943678974803871</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.05795653325116323</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>64</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6228,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6711,7 +6035,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6721,7 +6045,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6732,13 +6056,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6747,26 +6075,24 @@
       <c r="K4" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>122</v>
+        <v>473</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="P4" t="n">
-        <v>121</v>
+        <v>473</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1140968231800305</v>
+        <v>0.2358000475790323</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05812151649835226</v>
+        <v>0.2358000475790323</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6775,9 +6101,11 @@
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2387280320547482</v>
+      </c>
       <c r="W4" t="n">
         <v>23</v>
       </c>
@@ -6785,37 +6113,33 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2845422957875736</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>44</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3977066626192765</v>
+        <v>0.4389257668474973</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.00424062952457778</v>
+        <v>0.1734379015561023</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02049482076161968</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>7</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
@@ -6832,7 +6156,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6863,7 +6187,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6872,24 +6196,26 @@
       <c r="K5" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>44071</v>
+      </c>
       <c r="M5" t="n">
-        <v>473</v>
+        <v>134</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="P5" t="n">
-        <v>473</v>
+        <v>133</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2358000475790323</v>
+        <v>0.1337956033151394</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.2358000475790323</v>
+        <v>0.0714035091145092</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6898,11 +6224,9 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2387280320547482</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
         <v>23</v>
       </c>
@@ -6910,33 +6234,37 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>56</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4389257668474973</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1734379015561023</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>19</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6953,7 +6281,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6971,24 +6299,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -6998,10 +6322,10 @@
         <v>43913</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>44071</v>
+        <v>44497</v>
       </c>
       <c r="M6" t="n">
-        <v>134</v>
+        <v>428</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>-0.3050371165491933</v>
@@ -7010,13 +6334,13 @@
         <v>-0.3050371165491933</v>
       </c>
       <c r="P6" t="n">
-        <v>133</v>
+        <v>427</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1337956033151394</v>
+        <v>0.1935926383665935</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.0714035091145092</v>
+        <v>0.1841739972069035</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7044,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>111</v>
+        <v>405</v>
       </c>
       <c r="AC6" t="n">
-        <v>56</v>
+        <v>350</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
@@ -7056,29 +6380,21 @@
         <v>0.4389257668474975</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.009041363091579158</v>
+        <v>0.1218118511839735</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>313</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.01328199261615694</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.02049482076161968</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -7090,7 +6406,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7121,7 +6437,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -7131,10 +6447,10 @@
         <v>43913</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>44497</v>
+        <v>44071</v>
       </c>
       <c r="M7" t="n">
-        <v>428</v>
+        <v>134</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>-0.3050371165491933</v>
@@ -7143,13 +6459,13 @@
         <v>-0.3050371165491933</v>
       </c>
       <c r="P7" t="n">
-        <v>427</v>
+        <v>133</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1935926383665935</v>
+        <v>0.1337956033151394</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1841739972069035</v>
+        <v>0.0714035091145092</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7177,10 +6493,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>405</v>
+        <v>111</v>
       </c>
       <c r="AC7" t="n">
-        <v>350</v>
+        <v>56</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
@@ -7189,13 +6505,13 @@
         <v>0.4389257668474975</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1218118511839735</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>313</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7215,7 +6531,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7233,24 +6549,20 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -7259,26 +6571,24 @@
       <c r="K8" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>44071</v>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>134</v>
+        <v>473</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>473</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1337956033151394</v>
+        <v>0.2293480979522207</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0714035091145092</v>
+        <v>0.2293480979522207</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7287,9 +6597,11 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.2233658966394274</v>
+      </c>
       <c r="W8" t="n">
         <v>23</v>
       </c>
@@ -7297,50 +6609,38 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>111</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>56</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.4389257668474984</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.009041363091579158</v>
+        <v>0.1669859519292907</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>19</v>
-      </c>
+        <v>-4.440892098500626e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.01328199261615694</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.02049482076161968</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -7352,7 +6652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7383,7 +6683,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -7392,24 +6692,26 @@
       <c r="K9" s="2" t="n">
         <v>43913</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>44071</v>
+      </c>
       <c r="M9" t="n">
-        <v>473</v>
+        <v>134</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="P9" t="n">
-        <v>473</v>
+        <v>133</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2293480979522207</v>
+        <v>0.1337956033151394</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2293480979522207</v>
+        <v>0.0714035091145092</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7418,11 +6720,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.2233658966394274</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
         <v>23</v>
       </c>
@@ -7430,33 +6730,37 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>56</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4389257668474984</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.1669859519292907</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-4.440892098500626e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>19</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7464,143 +6768,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M10" t="n">
-        <v>134</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P10" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1337956033151394</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.0714035091145092</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>111</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>56</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.4389257668474975</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.009041363091579158</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.01328199261615694</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.02049482076161968</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7613,7 +6780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8096,7 +7263,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8106,7 +7273,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8117,41 +7284,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>44729</v>
+        <v>44848</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>45316</v>
+        <v>45440</v>
       </c>
       <c r="M4" t="n">
-        <v>517</v>
+        <v>602</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2546372012998201</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2645312178855237</v>
       </c>
       <c r="P4" t="n">
-        <v>516</v>
+        <v>539</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1197495450449226</v>
+        <v>0.1893416657019125</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09727560120458689</v>
+        <v>0.1659472351931517</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
@@ -8164,40 +7335,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="X4" t="n">
-        <v>-80</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2546372012998201</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.2645312178855237</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AC4" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2849153424233462</v>
+        <v>0.341628535451294</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0426061552072739</v>
+        <v>0.02606547878129092</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.07739321627689422</v>
+        <v>0.04449462530917325</v>
       </c>
       <c r="AH4" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8206,8 +7377,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.8811234607151575</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.4676866206072701</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8217,7 +7392,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8248,35 +7423,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>44848</v>
+        <v>44995</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>45440</v>
+        <v>45427</v>
       </c>
       <c r="M5" t="n">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2546372012998201</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2645312178855237</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="P5" t="n">
-        <v>539</v>
+        <v>593</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1893416657019125</v>
+        <v>0.1916767325892264</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1659472351931517</v>
+        <v>0.1668756814077786</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
@@ -8289,40 +7464,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2546372012998201</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2645312178855237</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>405</v>
+        <v>297</v>
       </c>
       <c r="AC5" t="n">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.341628535451294</v>
+        <v>0.4556267130138261</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.02606547878129092</v>
+        <v>0.02699392499591777</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.04449462530917325</v>
+        <v>-0.01387885733927396</v>
       </c>
       <c r="AH5" t="n">
-        <v>152</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8335,7 +7510,7 @@
         <v>0.8811234607151575</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.4676866206072701</v>
+        <v>-0.1500721998113352</v>
       </c>
     </row>
     <row r="6">
@@ -8346,7 +7521,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8364,52 +7539,48 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>44995</v>
+        <v>44628</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45427</v>
+        <v>45063</v>
       </c>
       <c r="M6" t="n">
-        <v>594</v>
+        <v>344</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="P6" t="n">
-        <v>593</v>
+        <v>343</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1916767325892264</v>
+        <v>0.0606958878044086</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1668756814077786</v>
+        <v>0.04023777774229433</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8422,62 +7593,50 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>297</v>
+        <v>44</v>
       </c>
       <c r="X6" t="n">
-        <v>102</v>
+        <v>-151</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AC6" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4556267130138261</v>
+        <v>0.195307510828868</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02699392499591777</v>
+        <v>-0.09964397866956645</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.01387885733927396</v>
+        <v>0.1357366257427034</v>
       </c>
       <c r="AH6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.06960008020319167</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.09127207361616818</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-105</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.1500721998113352</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8487,7 +7646,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8518,35 +7677,35 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>44564</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>44628</v>
+        <v>44729</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45063</v>
+        <v>45125</v>
       </c>
       <c r="M7" t="n">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="P7" t="n">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.0606958878044086</v>
+        <v>0.1523970119809249</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.04023777774229433</v>
+        <v>0.1068649472994739</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8559,40 +7718,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>44</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>-151</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AC7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.195307510828868</v>
+        <v>0.3117487371803249</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.09964397866956645</v>
+        <v>-0.03301680911238693</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1357366257427034</v>
+        <v>0.06147294549549165</v>
       </c>
       <c r="AH7" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8612,7 +7771,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8630,116 +7789,104 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45125</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>385</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="P8" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1523970119809249</v>
+        <v>0.01299867294183905</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1068649472994739</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-80</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>50</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3117487371803249</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03301680911238693</v>
+        <v>-0.1398817564118608</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.06147294549549165</v>
+        <v>0.2991318266089934</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>-253</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.009589346094886972</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.01592027078140257</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-132</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.1877889693631971</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.1579827546099043</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8749,7 +7896,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8780,77 +7927,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45309</v>
+      </c>
       <c r="M9" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.01299867294183905</v>
+        <v>0.1210803898573113</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.09788083483191509</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>-80</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>397</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>177</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.2849153424233462</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1398817564118608</v>
+        <v>-0.0420009215799457</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2991318266089934</v>
+        <v>0.07739321627689422</v>
       </c>
       <c r="AH9" t="n">
-        <v>-253</v>
+        <v>144</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8863,147 +8014,6 @@
         <v>0.1877889693631971</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.1579827546099043</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45309</v>
-      </c>
-      <c r="M10" t="n">
-        <v>512</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="P10" t="n">
-        <v>511</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1210803898573113</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09788083483191509</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>115</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-80</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>397</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>177</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2849153424233462</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.0420009215799457</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.07739321627689422</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>144</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.0006052336273282</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.07570585866239699</v>
       </c>
     </row>
@@ -9018,7 +8028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9501,7 +8511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9511,7 +8521,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9522,87 +8532,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45911</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.06042568392595738</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.0487682868766525</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>52</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.01725642090524599</v>
+        <v>-0.06602470778189849</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>0.1977751279185385</v>
       </c>
       <c r="AH4" t="n">
-        <v>31</v>
+        <v>-76</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9611,8 +8621,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9622,7 +8636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9653,77 +8667,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45911</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.06042568392595738</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.0487682868766525</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>52</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243419</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>-0.01725642090524599</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.07322206722135982</v>
       </c>
       <c r="AH5" t="n">
-        <v>-76</v>
+        <v>31</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9736,7 +8754,7 @@
         <v>0.1692510023843161</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.08068656438877009</v>
       </c>
     </row>
     <row r="6">
@@ -9747,7 +8765,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9765,119 +8783,103 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45911</v>
-      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>141</v>
+        <v>88</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06042568392595738</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.0487682868766525</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>52</v>
+        <v>-55</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01725642090524599</v>
+        <v>-0.06602470778189849</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>0.1977751279185385</v>
       </c>
       <c r="AH6" t="n">
-        <v>31</v>
+        <v>-76</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.04615004753547058</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.03928937762398355</v>
       </c>
     </row>
     <row r="7">
@@ -9888,7 +8890,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9919,77 +8921,81 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45897</v>
+      </c>
       <c r="M7" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.05476215413481124</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0</v>
+        <v>0.04277382585638228</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>43</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243419</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>-0.02325088192551621</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.07322206722135982</v>
       </c>
       <c r="AH7" t="n">
-        <v>-76</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10002,7 +9008,7 @@
         <v>0.04615004753547058</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.03928937762398355</v>
+        <v>0.02142863298018183</v>
       </c>
     </row>
     <row r="8">
@@ -10013,7 +9019,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10031,119 +9037,103 @@
           <t>mvo_t_10_lw</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45897</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05476215413481124</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.04277382585638228</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>43</v>
+        <v>-55</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02325088192551621</v>
+        <v>-0.06602470778189849</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>0.1977751279185385</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>-76</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>-0.005994461020270223</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>0.04615004753547058</v>
+        <v>0.1692510023843161</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.02142863298018183</v>
+        <v>-0.1307501836098439</v>
       </c>
     </row>
     <row r="9">
@@ -10154,7 +9144,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10185,77 +9175,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45897</v>
+      </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.05476215413481124</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.04277382585638228</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.1245530606971786</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>43</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.1422736834243419</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>-0.02325088192551621</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.07322206722135982</v>
       </c>
       <c r="AH9" t="n">
-        <v>-76</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10268,147 +9262,6 @@
         <v>0.1692510023843161</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.1307501836098439</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>mvo</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="M10" t="n">
-        <v>132</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="P10" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.05476215413481124</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.04277382585638228</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>98</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>43</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1422736834243419</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.02325088192551621</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.07322206722135982</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>-0.005994461020270223</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1692510023843161</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>-0.08068656438877009</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_quarterly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_mvo_quarterly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.176783790375948</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.7623511595632295</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.7620015542055643</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,51 +1347,51 @@
         <v>1.609526515663447</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,51 +1496,51 @@
         <v>1.318760445859326</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1644,51 +1645,51 @@
         <v>0.6288201485162133</v>
       </c>
       <c r="AD8" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>6/7</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH8" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
       <c r="AJ8" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>3/5</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,51 +1794,51 @@
         <v>0.9834344794881269</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.09032004823014436</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.265757517207872</v>
+        <v>0.04076898034342898</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908825</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791229</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441406</v>
+        <v>-0.1697286534192363</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493455</v>
+        <v>0.2044255219913531</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,66 +2252,68 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+        <v>36076</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>36119</v>
+      </c>
       <c r="M3" t="n">
-        <v>1896</v>
+        <v>89</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.5314111816834861</v>
+        <v>-0.1801769586891863</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="P3" t="n">
-        <v>1889</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.3261125795445277</v>
+        <v>0.09633253677130151</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.3261125795445277</v>
+        <v>0.0442262701206608</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>-0.06880676405722819</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>58</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>27</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.5314111816834861</v>
+        <v>-0.1801769586891863</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.5405779751541202</v>
+        <v>-0.1840536062106816</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-24</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.134067141406985</v>
+        <v>0.2197754266592722</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2316,9 +2321,11 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
       <c r="AI3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -2370,72 +2377,72 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36880</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>38922</v>
-      </c>
+        <v>36038</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>1591</v>
+        <v>426</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2056920481641104</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.1796087057389839</v>
       </c>
       <c r="P4" t="n">
-        <v>1583</v>
+        <v>425</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1543707126316287</v>
+        <v>0.1194500793427242</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1414173762065351</v>
+        <v>0.1194500793427242</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.02844057336797046</v>
+      </c>
       <c r="W4" t="n">
-        <v>189</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-449</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2056920481641104</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2212307393619097</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1402</v>
+        <v>395</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2589575588267659</v>
+        <v>0.203300994945913</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1846952033379927</v>
+        <v>0.07522380922206336</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3257191335193758</v>
+        <v>0.01122422300641457</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
@@ -2491,34 +2498,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38958</v>
+        <v>36116</v>
       </c>
       <c r="M5" t="n">
-        <v>1617</v>
+        <v>86</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.4211034935649058</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="P5" t="n">
-        <v>1609</v>
+        <v>84</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2150499661001916</v>
+        <v>0.08770963218134382</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.1986071921955756</v>
+        <v>0.03959068158620798</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2528,39 +2535,43 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.4211034935649058</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.4324281870017384</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1034</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.7274244858689951</v>
+        <v>0.203300994945913</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1275053873489521</v>
+        <v>-0.004635588534452818</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1103076881185803</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>0.01122422300641457</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -2612,76 +2623,80 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>36397</v>
+      </c>
       <c r="M6" t="n">
-        <v>1896</v>
+        <v>279</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.6091181530671368</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="P6" t="n">
-        <v>1889</v>
+        <v>277</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.4367609404936754</v>
+        <v>0.1066258625293515</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.4367609404936754</v>
+        <v>0.08634309966117983</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.2595369962595653</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.6091181530671368</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.6167647998119878</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>248</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>193</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1.558317834012275</v>
+        <v>0.203300994945913</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.1106483609491477</v>
+        <v>0.04211682954051903</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-0.07770697138365068</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0.01122422300641457</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>217</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -2733,76 +2748,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5601026635225388</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="P7" t="n">
-        <v>1889</v>
+        <v>84</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3387659126715243</v>
+        <v>0.08770963218134382</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3387659126715243</v>
+        <v>0.03959068158620798</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.08001949728659474</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5601026635225388</v>
+        <v>-0.1689527356827717</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.5687081783665724</v>
+        <v>-0.172882458507236</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.273257683275917</v>
+        <v>0.203300994945913</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.01265333312699657</v>
+        <v>-0.004635588534452818</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.02869148183905268</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0.01122422300641457</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -2854,83 +2873,87 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>37838</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1896</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.3560213736027806</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3860586751023685</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1766</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2569514384238935</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2569514384238935</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.02047746840375408</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>206</v>
+        <v>-31</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3560213736027806</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3860586751023685</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1052</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.5528465682076524</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.06916114112063426</v>
+        <v>-0.0442262701206608</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1753898080807055</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0.1801769586891863</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-31</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.04814722243458536</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.04405046681985514</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2975,34 +2998,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>39066</v>
+        <v>36104</v>
       </c>
       <c r="M9" t="n">
-        <v>1693</v>
+        <v>78</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.4659826112756107</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.4958240313246576</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="P9" t="n">
-        <v>1597</v>
+        <v>77</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.2604511098226162</v>
+        <v>0.08537443726210804</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.2461213280970662</v>
+        <v>0.03672209605100416</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3012,46 +3035,54 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4659826112756107</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4958240313246576</v>
+        <v>-0.1588454086617709</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1110</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.8725981983259128</v>
+        <v>0.1888421109478304</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.07999125144746153</v>
+        <v>-0.007504174069656637</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06542857040787542</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.02133155002741538</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>16</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.04814722243458536</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.01572483169298367</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3348,68 +3379,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441406</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027504</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573126</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286764</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922728</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388244</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459472</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573126</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286764</v>
+        <v>-0.4862309442441406</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616542</v>
+        <v>0.94639982458421</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3457,68 +3486,66 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.5344887685426145</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.5405779751541202</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.3261985683606681</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.3261985683606681</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40568</v>
-      </c>
-      <c r="M3" t="n">
-        <v>830</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4418768397766436</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4486552572799976</v>
-      </c>
-      <c r="P3" t="n">
-        <v>815</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2132143827670934</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1170148981982912</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
-      </c>
-      <c r="V3" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>-0.07492263356632722</v>
+      </c>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4418768397766436</v>
+        <v>-0.5344887685426145</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4486552572799976</v>
+        <v>-0.5405779751541202</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>475</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-385</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.7917192320057245</v>
+        <v>1.148175881534113</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3526,11 +3553,9 @@
       <c r="AG3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
       <c r="AK3" s="3" t="inlineStr"/>
@@ -3582,34 +3607,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36880</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38923</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1591</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2109088856538605</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2212307393619097</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1588</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1543710234256555</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1414549496924858</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>41061</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.08555079627746587</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1365494988551755</v>
-      </c>
-      <c r="P4" t="n">
-        <v>249</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.04332405449145316</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.02870286938692595</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3619,54 +3644,46 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>1171</v>
+        <v>188</v>
       </c>
       <c r="X4" t="n">
-        <v>816</v>
+        <v>-449</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.08555079627746587</v>
+        <v>-0.2109088856538605</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1365494988551755</v>
+        <v>-0.2212307393619097</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>39</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-821</v>
-      </c>
+        <v>1403</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.0935544543417024</v>
+        <v>0.2672807763506813</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.08831202881136521</v>
+        <v>-0.1847436186681823</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3563260434991777</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-436</v>
-      </c>
+        <v>0.3235798828887541</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.1079725986742808</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3711,34 +3728,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38986</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1635</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.4249055567199778</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.4324281870017382</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1632</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.213881505245561</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1986761406376901</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40486</v>
-      </c>
-      <c r="M5" t="n">
-        <v>775</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3674998761946072</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3674998761946072</v>
-      </c>
-      <c r="P5" t="n">
-        <v>774</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1532547245176266</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.08127722777506252</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3748,54 +3765,46 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4249055567199778</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3674998761946072</v>
+        <v>-0.4324281870017382</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>420</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-440</v>
-      </c>
+        <v>1053</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.5810273585142876</v>
+        <v>0.7388448309403761</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.03573767042322865</v>
+        <v>-0.127522427722978</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.07437696358203638</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-55</v>
-      </c>
+        <v>0.1095832118226368</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1475930532307546</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.007539848144645811</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3840,80 +3849,76 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.6116853778675797</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.6167647998119878</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.4368761048834142</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.4368761048834142</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40095</v>
-      </c>
-      <c r="M6" t="n">
-        <v>505</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2253489755584758</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2347571285205642</v>
-      </c>
-      <c r="P6" t="n">
-        <v>490</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06488886565424552</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.0277887870264453</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.2644001921381384</v>
+      </c>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2253489755584758</v>
+        <v>-0.6116853778675797</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2347571285205642</v>
+        <v>-0.6167647998119878</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-710</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2909038630923371</v>
+        <v>1.5752313794122</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.08922611117184587</v>
+        <v>0.1106775365227461</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2165278642181678</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>-325</v>
-      </c>
+        <v>-0.07719660932496519</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -3965,80 +3970,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5629918111274099</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5687081783665724</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1893</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.3388552378972484</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.3388552378972484</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40449</v>
-      </c>
-      <c r="M7" t="n">
-        <v>748</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3639842631607436</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3717086876431007</v>
-      </c>
-      <c r="P7" t="n">
-        <v>733</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1500396731487487</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.0781755900741586</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.08606172406438461</v>
+      </c>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3639842631607436</v>
+        <v>-0.5629918111274099</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3717086876431007</v>
+        <v>-0.5687081783665724</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>393</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-467</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.5722881401796749</v>
+        <v>1.288286639616152</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03883930812413257</v>
+        <v>0.01265666953658034</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.07789257661589999</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-82</v>
-      </c>
+        <v>-0.02850304258479541</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4090,80 +4091,76 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37838</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.3602508816078583</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3860586751023684</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1801</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2570191909467384</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2570191909467384</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>39428</v>
-      </c>
-      <c r="M8" t="n">
-        <v>45</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.05542135568040074</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.06689328315495324</v>
-      </c>
-      <c r="P8" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.03285628964813481</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.004242497392177237</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.02691075394883213</v>
+      </c>
       <c r="W8" t="n">
-        <v>33</v>
+        <v>843</v>
       </c>
       <c r="X8" t="n">
-        <v>-322</v>
+        <v>206</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.05542135568040074</v>
+        <v>-0.3602508816078583</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.06689328315495324</v>
+        <v>-0.3860586751023684</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-848</v>
-      </c>
+        <v>1052</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.05867309833192547</v>
+        <v>0.5631127441226709</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.1127724008061139</v>
+        <v>-0.06917937741392965</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.3864554840962429</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-463</v>
-      </c>
+        <v>0.1742378869347562</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -4215,34 +4212,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>39192</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1776</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.4694899183940108</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.4958240313246576</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1696</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.2547924669232837</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.2466670449883579</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40445</v>
-      </c>
-      <c r="M9" t="n">
-        <v>746</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3561271102519856</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3639469600214459</v>
-      </c>
-      <c r="P9" t="n">
-        <v>731</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1489538204488156</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.07750613802078468</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4252,43 +4249,39 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3561271102519856</v>
+        <v>-0.4694899183940108</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3639469600214459</v>
+        <v>-0.4958240313246576</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>391</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-469</v>
-      </c>
+        <v>1194</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.5531015762930465</v>
+        <v>0.8849783155350133</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.03950876017750649</v>
+        <v>-0.0795315233723102</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.08574972952465798</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-84</v>
-      </c>
+        <v>0.06499885014860374</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -4592,34 +4585,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856398</v>
+        <v>0.2354171526922728</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687868</v>
+        <v>0.1563175570682493</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4629,22 +4622,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665691</v>
+        <v>-0.5035092528573126</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286764</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4653,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160748</v>
+        <v>1.014136226616542</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4701,34 +4694,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43577</v>
+        <v>40568</v>
       </c>
       <c r="M3" t="n">
-        <v>144</v>
+        <v>830</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766436</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="P3" t="n">
-        <v>138</v>
+        <v>815</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.0794670201188962</v>
+        <v>0.2132143827670934</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.05085917347920408</v>
+        <v>0.1170361099990996</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4738,31 +4731,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.4418768397766436</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.4486552572799976</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>80</v>
+        <v>475</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>-385</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.7917192320057245</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4826,34 +4819,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>41061</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43578</v>
+        <v>41117</v>
       </c>
       <c r="M4" t="n">
-        <v>145</v>
+        <v>1210</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1968052513911283</v>
+        <v>-0.08555079627746587</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="P4" t="n">
-        <v>139</v>
+        <v>249</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.07990143847314349</v>
+        <v>0.04332405449145316</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05131323495950512</v>
+        <v>0.02870807248121086</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4863,40 +4856,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>1171</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1968052513911283</v>
+        <v>-0.08555079627746587</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1971519721341342</v>
+        <v>-0.1365494988551755</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>-821</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2450280604199588</v>
+        <v>0.0935544543417024</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.0004540614803010407</v>
+        <v>-0.0883280375178887</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>-0.003799503415698791</v>
+        <v>0.3563260434991777</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>-436</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4906,10 +4899,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.2004725031597112</v>
+        <v>0.1475930532307546</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.1592411666562514</v>
+        <v>-0.1079725986742808</v>
       </c>
     </row>
     <row r="5">
@@ -4955,34 +4948,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43588</v>
+        <v>40486</v>
       </c>
       <c r="M5" t="n">
-        <v>153</v>
+        <v>775</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="P5" t="n">
-        <v>152</v>
+        <v>774</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.08303743446013791</v>
+        <v>0.1532547245176266</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.05476872768330868</v>
+        <v>0.0812919612525288</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4992,40 +4985,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2026163801193157</v>
+        <v>-0.3674998761946072</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>89</v>
+        <v>420</v>
       </c>
       <c r="AC5" t="n">
-        <v>13</v>
+        <v>-440</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2541015078158164</v>
+        <v>0.5810273585142876</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.003909554204104604</v>
+        <v>-0.03574414874657077</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.009610632143886244</v>
+        <v>0.07437696358203638</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>-55</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5035,10 +5028,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.2004725031597112</v>
+        <v>0.1475930532307546</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.01980775507866428</v>
+        <v>-0.007539848144645811</v>
       </c>
     </row>
     <row r="6">
@@ -5084,34 +5077,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43815</v>
+        <v>40095</v>
       </c>
       <c r="M6" t="n">
-        <v>310</v>
+        <v>505</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="P6" t="n">
-        <v>304</v>
+        <v>490</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.09948481923745864</v>
+        <v>0.06488886565424552</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.0932471095787893</v>
+        <v>0.02779382442103512</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5121,40 +5114,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.2253489755584758</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.2347571285205642</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c r="AC6" t="n">
-        <v>170</v>
+        <v>-710</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.2909038630923371</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.04238793609958522</v>
+        <v>-0.08924228557806445</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.2165278642181678</v>
       </c>
       <c r="AH6" t="n">
-        <v>166</v>
+        <v>-325</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -5209,34 +5202,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43655</v>
+        <v>40449</v>
       </c>
       <c r="M7" t="n">
-        <v>198</v>
+        <v>748</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="P7" t="n">
-        <v>192</v>
+        <v>733</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07880862330706591</v>
+        <v>0.1500396731487487</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05908791263210079</v>
+        <v>0.07818976130423497</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5246,40 +5239,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3639842631607436</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3717086876431007</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>134</v>
+        <v>393</v>
       </c>
       <c r="AC7" t="n">
-        <v>58</v>
+        <v>-467</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.5722881401796749</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.008228739152896715</v>
+        <v>-0.0388463486948646</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.07789257661589999</v>
       </c>
       <c r="AH7" t="n">
-        <v>54</v>
+        <v>-82</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5334,34 +5327,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43815</v>
+        <v>39428</v>
       </c>
       <c r="M8" t="n">
-        <v>310</v>
+        <v>45</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1930057479754296</v>
+        <v>-0.05542135568040074</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>37</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.09948481923745901</v>
+        <v>0.03285628964813481</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.09324710957878965</v>
+        <v>0.004243266448177786</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5371,40 +5364,40 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1930057479754296</v>
+        <v>-0.05542135568040074</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.196417529389515</v>
+        <v>-0.06689328315495324</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>246</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="n">
-        <v>170</v>
+        <v>-848</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.239166199128706</v>
+        <v>0.05867309833192547</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.04238793609958557</v>
+        <v>-0.1127928435509218</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0.3864554840962429</v>
       </c>
       <c r="AH8" t="n">
-        <v>166</v>
+        <v>-463</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -5459,34 +5452,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43655</v>
+        <v>40445</v>
       </c>
       <c r="M9" t="n">
-        <v>198</v>
+        <v>746</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3561271102519856</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="P9" t="n">
-        <v>192</v>
+        <v>731</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.07880862330706591</v>
+        <v>0.1489538204488156</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05908791263210079</v>
+        <v>0.07752018789636837</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5496,40 +5489,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1930057479754295</v>
+        <v>-0.3561271102519856</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1964175293895148</v>
+        <v>-0.3639469600214459</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>134</v>
+        <v>391</v>
       </c>
       <c r="AC9" t="n">
-        <v>58</v>
+        <v>-469</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2391661991287057</v>
+        <v>0.5531015762930465</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.008228739152896715</v>
+        <v>-0.03951592210273119</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.08574972952465798</v>
       </c>
       <c r="AH9" t="n">
-        <v>54</v>
+        <v>-84</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5836,34 +5829,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606708</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860072</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428324</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049073</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5873,22 +5866,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606708</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.2022979914860072</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5897,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320053</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5945,34 +5938,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M3" t="n">
+        <v>146</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1950653726524902</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1964175293895147</v>
+      </c>
+      <c r="P3" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.07892753856493077</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05078939621381112</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44046</v>
-      </c>
-      <c r="M3" t="n">
-        <v>115</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P3" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1260611393681861</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06236214602293004</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5982,31 +5975,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AC3" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2423369128686717</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6070,83 +6063,91 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43578</v>
+      </c>
+      <c r="M4" t="n">
+        <v>146</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.196736784489579</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.197151972134134</v>
+      </c>
+      <c r="P4" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.07962920109406921</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05124091182989079</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>473</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.3050371165491932</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.3050371165491932</v>
-      </c>
-      <c r="P4" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.2358000475790323</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.2358000475790323</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>-0.2387280320547482</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.196736784489579</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3050371165491932</v>
+        <v>-0.197151972134134</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4389257668474973</v>
+        <v>0.2449219392731257</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.1734379015561023</v>
+        <v>0.0004515156160796729</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>-0.001671411837088743</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
       <c r="AI4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.2035442094916755</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1614584458581432</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6191,34 +6192,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43588</v>
+      </c>
+      <c r="M5" t="n">
+        <v>154</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2007936180365936</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2026163801193158</v>
+      </c>
+      <c r="P5" t="n">
+        <v>152</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.08276913833241978</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05469153423031017</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M5" t="n">
-        <v>134</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P5" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1337956033151394</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.0714035091145092</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6228,40 +6229,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.2007936180365936</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.2026163801193158</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="AC5" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2512412595396258</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.009041363091579158</v>
+        <v>0.003902138016499059</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>-0.005728245384103325</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -6270,8 +6271,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.2035442094916755</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.02453925236218701</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6316,34 +6321,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43815</v>
+      </c>
+      <c r="M6" t="n">
+        <v>311</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1950653726524902</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1964175293895147</v>
+      </c>
+      <c r="P6" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.0993263693371941</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.0931167225335139</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44497</v>
-      </c>
-      <c r="M6" t="n">
-        <v>428</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P6" t="n">
-        <v>427</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1935926383665935</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1841739972069035</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -6353,40 +6358,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>405</v>
+        <v>246</v>
       </c>
       <c r="AC6" t="n">
-        <v>350</v>
+        <v>168</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2423369128686717</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.1218118511839735</v>
+        <v>0.04232732631970278</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -6441,34 +6446,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43656</v>
+      </c>
+      <c r="M7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1950653726524902</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1964175293895147</v>
+      </c>
+      <c r="P7" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.07841774054300285</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05900627200861279</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M7" t="n">
-        <v>134</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P7" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1337956033151394</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.0714035091145092</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6478,40 +6483,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="AC7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2423369128686717</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.009041363091579158</v>
+        <v>0.008216875794801674</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6566,76 +6571,80 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43815</v>
+      </c>
+      <c r="M8" t="n">
+        <v>311</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1950653726524904</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1964175293895148</v>
+      </c>
+      <c r="P8" t="n">
+        <v>308</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.09932636933719448</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.09311672253351425</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>473</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.3050371165491937</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.3050371165491937</v>
-      </c>
-      <c r="P8" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2293480979522207</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.2293480979522207</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.2233658966394274</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.1950653726524904</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3050371165491937</v>
+        <v>-0.1964175293895148</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>168</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4389257668474984</v>
+        <v>0.2423369128686719</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.1669859519292907</v>
+        <v>0.04232732631970313</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-4.440892098500626e-16</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>-1.110223024625157e-16</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>165</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -6687,34 +6696,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43656</v>
+      </c>
+      <c r="M9" t="n">
+        <v>200</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1950653726524902</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1964175293895147</v>
+      </c>
+      <c r="P9" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.07841774054300285</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05900627200861279</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44071</v>
-      </c>
-      <c r="M9" t="n">
-        <v>134</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.3050371165491933</v>
-      </c>
-      <c r="P9" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1337956033151394</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.0714035091145092</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6724,40 +6733,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1950653726524902</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3050371165491933</v>
+        <v>-0.1964175293895147</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="AC9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4389257668474975</v>
+        <v>0.2423369128686717</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.009041363091579158</v>
+        <v>0.008216875794801674</v>
       </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7064,34 +7073,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428744</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7101,22 +7110,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428744</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7125,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088533</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7173,34 +7182,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44046</v>
+      </c>
+      <c r="M3" t="n">
+        <v>115</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="P3" t="n">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1260611393681861</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06236214602293004</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45300</v>
-      </c>
-      <c r="M3" t="n">
-        <v>506</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2991318266089934</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2991318266089934</v>
-      </c>
-      <c r="P3" t="n">
-        <v>505</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1740571730122129</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1398817564118608</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7210,31 +7219,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2991318266089934</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>253</v>
+        <v>92</v>
       </c>
       <c r="AC3" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4268018408678846</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7298,91 +7307,83 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>473</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.3050371165491932</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.3050371165491932</v>
+      </c>
+      <c r="P4" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.2358000475790323</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.2358000475790323</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45440</v>
-      </c>
-      <c r="M4" t="n">
-        <v>602</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2546372012998201</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2645312178855237</v>
-      </c>
-      <c r="P4" t="n">
-        <v>539</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1893416657019125</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1659472351931517</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>-0.2387280320547482</v>
+      </c>
       <c r="W4" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2546372012998201</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2645312178855237</v>
+        <v>-0.3050371165491932</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>405</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>185</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.341628535451294</v>
+        <v>0.4389257668474973</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.02606547878129092</v>
+        <v>0.1734379015561023</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.04449462530917325</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>152</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" s="3" t="inlineStr"/>
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.4676866206072701</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7427,34 +7428,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M5" t="n">
+        <v>134</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="P5" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1337956033151394</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.0714035091145092</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45427</v>
-      </c>
-      <c r="M5" t="n">
-        <v>594</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3130106839482674</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3130106839482674</v>
-      </c>
-      <c r="P5" t="n">
-        <v>593</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1916767325892264</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1668756814077786</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7464,40 +7465,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>297</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3130106839482674</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="AC5" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4556267130138261</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.02699392499591777</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-0.01387885733927396</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7506,12 +7507,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.8811234607151575</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.1500721998113352</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7556,34 +7553,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44497</v>
+      </c>
+      <c r="M6" t="n">
+        <v>428</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="P6" t="n">
+        <v>427</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1935926383665935</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1841739972069035</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44628</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45063</v>
-      </c>
-      <c r="M6" t="n">
-        <v>344</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.16339520086629</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.16339520086629</v>
-      </c>
-      <c r="P6" t="n">
-        <v>343</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.0606958878044086</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04023777774229433</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7593,40 +7590,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.16339520086629</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="AC6" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.195307510828868</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.09964397866956645</v>
+        <v>0.1218118511839735</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1357366257427034</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>47</v>
+        <v>313</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7681,34 +7678,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M7" t="n">
+        <v>134</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="P7" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1337956033151394</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.0714035091145092</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45125</v>
-      </c>
-      <c r="M7" t="n">
-        <v>385</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2376588811135018</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2376588811135018</v>
-      </c>
-      <c r="P7" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1523970119809249</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1068649472994739</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7718,40 +7715,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2376588811135018</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>270</v>
+        <v>111</v>
       </c>
       <c r="AC7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3117487371803249</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03301680911238693</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.06147294549549165</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7806,87 +7803,83 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>513</v>
+        <v>473</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.07611122125507064</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>473</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.01299867294183905</v>
+        <v>0.2293480979522207</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>0.2293480979522207</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
         <v>1</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="n">
+        <v>-0.2233658966394274</v>
+      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0.3050371165491937</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-220</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0</v>
+        <v>0.4389257668474984</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.1398817564118608</v>
+        <v>0.1669859519292907</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2991318266089934</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-253</v>
-      </c>
+        <v>-4.440892098500626e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.1579827546099043</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7931,34 +7924,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44071</v>
+      </c>
+      <c r="M9" t="n">
+        <v>134</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3050371165491933</v>
+      </c>
+      <c r="P9" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1337956033151394</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.0714035091145092</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44729</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45309</v>
-      </c>
-      <c r="M9" t="n">
-        <v>512</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2217386103320992</v>
-      </c>
-      <c r="P9" t="n">
-        <v>511</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1210803898573113</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09788083483191509</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -7968,40 +7961,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2217386103320992</v>
+        <v>-0.3050371165491933</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>397</v>
+        <v>111</v>
       </c>
       <c r="AC9" t="n">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2849153424233462</v>
+        <v>0.4389257668474975</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.0420009215799457</v>
+        <v>0.009041363091579158</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.07739321627689422</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8010,12 +8003,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.1877889693631971</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.07570585866239699</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8312,34 +8301,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428744</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451831</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8349,22 +8338,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428744</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8373,7 +8362,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8421,34 +8410,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="M3" t="n">
+        <v>506</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2991318266089934</v>
+      </c>
+      <c r="P3" t="n">
+        <v>505</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1740571730122129</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1398817564118608</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45751</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M3" t="n">
-        <v>108</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1977751279185385</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1977751279185385</v>
-      </c>
-      <c r="P3" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09337303719688129</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06602470778189849</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8458,31 +8447,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>58</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1977751279185385</v>
+        <v>-0.2991318266089934</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1977751279185385</v>
+        <v>-0.2991318266089934</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="AC3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2465332786371843</v>
+        <v>0.4268018408678846</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8546,73 +8535,77 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45440</v>
+      </c>
+      <c r="M4" t="n">
+        <v>602</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2546372012998201</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2645312178855237</v>
+      </c>
+      <c r="P4" t="n">
+        <v>539</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1893416657019125</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1659472351931517</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>88</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X4" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0.2546372012998201</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0.2645312178855237</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="AC4" t="n">
-        <v>-55</v>
+        <v>185</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0</v>
+        <v>0.341628535451294</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>0.02606547878129092</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.04449462530917325</v>
       </c>
       <c r="AH4" t="n">
-        <v>-76</v>
+        <v>152</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8622,10 +8615,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.8811234607151575</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.4676866206072701</v>
       </c>
     </row>
     <row r="5">
@@ -8671,34 +8664,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45427</v>
+      </c>
+      <c r="M5" t="n">
+        <v>594</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3130106839482674</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3130106839482674</v>
+      </c>
+      <c r="P5" t="n">
+        <v>593</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1916767325892264</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1668756814077786</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45911</v>
-      </c>
-      <c r="M5" t="n">
-        <v>141</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="P5" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.06042568392595738</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.0487682868766525</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -8708,40 +8701,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>34</v>
+        <v>297</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.3130106839482674</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>107</v>
+        <v>297</v>
       </c>
       <c r="AC5" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0.4556267130138261</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.01725642090524599</v>
+        <v>0.02699392499591777</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>-0.01387885733927396</v>
       </c>
       <c r="AH5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8751,10 +8744,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.8811234607151575</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.1500721998113352</v>
       </c>
     </row>
     <row r="6">
@@ -8800,73 +8793,77 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44628</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45063</v>
+      </c>
+      <c r="M6" t="n">
+        <v>344</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.16339520086629</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.16339520086629</v>
+      </c>
+      <c r="P6" t="n">
+        <v>343</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.0606958878044086</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04023777774229433</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>88</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="X6" t="n">
-        <v>-34</v>
+        <v>-151</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0.16339520086629</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC6" t="n">
-        <v>-55</v>
+        <v>80</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0</v>
+        <v>0.195307510828868</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>-0.09964397866956645</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.1357366257427034</v>
       </c>
       <c r="AH6" t="n">
-        <v>-76</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -8875,12 +8872,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.04615004753547058</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.03928937762398355</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8925,34 +8918,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45125</v>
+      </c>
+      <c r="M7" t="n">
+        <v>385</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2376588811135018</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2376588811135018</v>
+      </c>
+      <c r="P7" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1523970119809249</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1068649472994739</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="M7" t="n">
-        <v>132</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="P7" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.05476215413481124</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.04277382585638228</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8962,40 +8955,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2376588811135018</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>98</v>
+        <v>270</v>
       </c>
       <c r="AC7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0.3117487371803249</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.02325088192551621</v>
+        <v>-0.03301680911238693</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>0.06147294549549165</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9004,12 +8997,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.04615004753547058</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>0.02142863298018183</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9054,30 +9043,30 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>-0.07611122125507064</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>0.01299867294183905</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -9090,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
@@ -9105,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
@@ -9114,13 +9103,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.06602470778189849</v>
+        <v>-0.1398817564118608</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1977751279185385</v>
+        <v>0.2991318266089934</v>
       </c>
       <c r="AH8" t="n">
-        <v>-76</v>
+        <v>-253</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -9130,10 +9119,10 @@
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.1877889693631971</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0.1307501836098439</v>
+        <v>-0.1579827546099043</v>
       </c>
     </row>
     <row r="9">
@@ -9179,34 +9168,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45309</v>
+      </c>
+      <c r="M9" t="n">
+        <v>512</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2217386103320992</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2217386103320992</v>
+      </c>
+      <c r="P9" t="n">
+        <v>511</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1210803898573113</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09788083483191509</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45897</v>
-      </c>
-      <c r="M9" t="n">
-        <v>132</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1245530606971786</v>
-      </c>
-      <c r="P9" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.05476215413481124</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.04277382585638228</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -9216,40 +9205,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1245530606971786</v>
+        <v>-0.2217386103320992</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>98</v>
+        <v>397</v>
       </c>
       <c r="AC9" t="n">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1422736834243419</v>
+        <v>0.2849153424233462</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.02325088192551621</v>
+        <v>-0.0420009215799457</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.07322206722135982</v>
+        <v>0.07739321627689422</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -9259,10 +9248,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.1692510023843161</v>
+        <v>0.1877889693631971</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.08068656438877009</v>
+        <v>-0.07570585866239699</v>
       </c>
     </row>
   </sheetData>
@@ -9276,7 +9265,1255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451831</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45751</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M3" t="n">
+        <v>108</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="P3" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09337303719688129</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06602470778189849</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>32</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1977751279185385</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2465332786371843</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>89</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.06602470778189849</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.1977751279185385</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="M5" t="n">
+        <v>141</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="P5" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06042568392595738</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.0487682868766525</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>34</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>107</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>52</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.1422736834243419</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.01725642090524599</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.07322206722135982</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.08068656438877009</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>89</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.06602470778189849</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.1977751279185385</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.04615004753547058</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.03928937762398355</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="M7" t="n">
+        <v>132</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="P7" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.05476215413481124</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.04277382585638228</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>98</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.1422736834243419</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.02325088192551621</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.07322206722135982</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.04615004753547058</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0.02142863298018183</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>89</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.06602470778189849</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.1977751279185385</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-76</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.1307501836098439</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="M9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="P9" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.05476215413481124</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.04277382585638228</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.1245530606971786</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>98</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.1422736834243419</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>-0.02325088192551621</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.07322206722135982</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.1692510023843161</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.08068656438877009</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9382,24 +10619,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9430,20 +10665,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7281976744186046</v>
+        <v>0.473655019412091</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -9477,23 +10712,23 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>-120</v>
+        <v>-131</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-57</v>
+        <v>523</v>
       </c>
       <c r="G4" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0.04137931034482759</v>
+        <v>0.7281976744186046</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9523,19 +10758,21 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-57</v>
+      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.04794520547945205</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -9568,24 +10805,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-132</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.3625730994152047</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9616,21 +10851,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-132</v>
+      </c>
       <c r="G7" t="n">
-        <v>94</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.3625730994152047</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9647,37 +10884,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>259</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>59</v>
-      </c>
+        <v>-94</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.1058171745152355</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -9704,27 +10939,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3204941860465116</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9751,25 +10984,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="3" t="n">
+        <v>0.1059345535219079</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9796,25 +11031,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3204941860465116</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9841,24 +11078,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>119</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -9888,27 +11123,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
       <c r="J13" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -9925,24 +11158,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -9952,10 +11185,10 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.313573407202216</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9972,37 +11205,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
+        <v>-30</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.4585755813953488</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -10029,25 +11262,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
-      </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10074,25 +11309,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>183</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0.3139212423738214</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10119,27 +11356,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-63</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>181</v>
+        <v>145</v>
       </c>
       <c r="G18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.7309941520467836</v>
+        <v>0.4585755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -10166,32 +11403,169 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>58</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
-        <v>1</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="G21" t="n">
+        <v>63</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.7309941520467836</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-94</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>94</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
